--- a/artifacts/tasama-hr/imported/demo-files/soudah/Soudah - Master Data.xlsx
+++ b/artifacts/tasama-hr/imported/demo-files/soudah/Soudah - Master Data.xlsx
@@ -5,13 +5,15 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Master Data" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Leavers 2026" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Company" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="601">
   <si>
     <t>Employee No</t>
   </si>
@@ -1751,6 +1753,69 @@
   </si>
   <si>
     <t>SA52 1022 0482 1074 6859 0026</t>
+  </si>
+  <si>
+    <t>Last Working Day</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>SDH-1065</t>
+  </si>
+  <si>
+    <t>Fadi Shawky</t>
+  </si>
+  <si>
+    <t>فادي شوقي</t>
+  </si>
+  <si>
+    <t>2418836027</t>
+  </si>
+  <si>
+    <t>Resignation</t>
+  </si>
+  <si>
+    <t>Legal name (English)</t>
+  </si>
+  <si>
+    <t>Soudah Development Company</t>
+  </si>
+  <si>
+    <t>Legal name (Arabic)</t>
+  </si>
+  <si>
+    <t>شركة السودة للتطوير</t>
+  </si>
+  <si>
+    <t>Trading name</t>
+  </si>
+  <si>
+    <t>Soudah Development</t>
+  </si>
+  <si>
+    <t>Commercial registration</t>
+  </si>
+  <si>
+    <t>1010000000</t>
+  </si>
+  <si>
+    <t>GOSI establishment number</t>
+  </si>
+  <si>
+    <t>500000000</t>
+  </si>
+  <si>
+    <t>Main bank</t>
+  </si>
+  <si>
+    <t>King Fahd Road, Riyadh</t>
+  </si>
+  <si>
+    <t>Sites</t>
+  </si>
+  <si>
+    <t>Soudah, Asir</t>
   </si>
 </sst>
 </file>
@@ -1760,7 +1825,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1772,6 +1837,9 @@
       <b/>
       <color rgb="FFFFFFFF"/>
     </font>
+    <font>
+      <b/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1782,7 +1850,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5B4636"/>
+        <fgColor rgb="FF321E1E"/>
       </patternFill>
     </fill>
   </fills>
@@ -1798,13 +1866,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8495,4 +8564,162 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="12" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C2" t="s">
+        <v>584</v>
+      </c>
+      <c r="D2" t="s">
+        <v>585</v>
+      </c>
+      <c r="E2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G2" s="1">
+        <v>44836</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46234</v>
+      </c>
+      <c r="I2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="32" style="6" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="B1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="B2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="B3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="B4" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="B5" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="B6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B8" t="s">
+        <v>600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>